--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.63737173560979</v>
+        <v>8.228572907036591</v>
       </c>
       <c r="D2" t="n">
-        <v>51.27083383758027</v>
+        <v>8.331510498606795</v>
       </c>
       <c r="E2" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F2" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.04050966665131</v>
+        <v>7.806582820830839</v>
       </c>
       <c r="D3" t="n">
-        <v>47.40415975359713</v>
+        <v>7.703175959959535</v>
       </c>
       <c r="E3" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F3" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.08683374239499</v>
+        <v>4.076610483139186</v>
       </c>
       <c r="D4" t="n">
-        <v>25.55885662062101</v>
+        <v>4.153314200850914</v>
       </c>
       <c r="E4" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F4" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>84.34212002242144</v>
+        <v>13.70559450364348</v>
       </c>
       <c r="D5" t="n">
-        <v>84.10234929054576</v>
+        <v>13.66663175971369</v>
       </c>
       <c r="E5" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F5" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>73.72135141409841</v>
+        <v>11.97971960479099</v>
       </c>
       <c r="D6" t="n">
-        <v>74.931434308875</v>
+        <v>12.17635807519219</v>
       </c>
       <c r="E6" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F6" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.50583081347339</v>
+        <v>5.769697507189425</v>
       </c>
       <c r="D7" t="n">
-        <v>35.04372783046362</v>
+        <v>5.694605772450338</v>
       </c>
       <c r="E7" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F7" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.10562657206309</v>
+        <v>6.354664317960253</v>
       </c>
       <c r="D8" t="n">
-        <v>38.82902664934083</v>
+        <v>6.309716830517885</v>
       </c>
       <c r="E8" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F8" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.589206768412444</v>
+        <v>1.070746099867022</v>
       </c>
       <c r="D9" t="n">
-        <v>24.35080273974099</v>
+        <v>3.957005445207911</v>
       </c>
       <c r="E9" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F9" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.50333972604078</v>
+        <v>0.5692927054816268</v>
       </c>
       <c r="D10" t="n">
-        <v>14.19170358686087</v>
+        <v>2.306151832864891</v>
       </c>
       <c r="E10" t="n">
-        <v>25.75116581903074</v>
+        <v>4.184564445592495</v>
       </c>
       <c r="F10" t="n">
-        <v>21.9874945169865</v>
+        <v>3.572967859010307</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
